--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Changes in Financial Assets_Liabilities of the Household Sector (At Current Prices).xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Changes in Financial Assets_Liabilities of the Household Sector (At Current Prices).xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
   <si>
     <t>Year</t>
   </si>
@@ -58,12 +58,15 @@
     <t>Changes in financial liabilities (12 to 15)</t>
   </si>
   <si>
+    <t xml:space="preserve">2024-25   </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t xml:space="preserve">2023-24   </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">2022-23   </t>
   </si>
   <si>
@@ -223,20 +226,22 @@
     <t xml:space="preserve">1970-71   </t>
   </si>
   <si>
-    <t xml:space="preserve">Notes :  1. Data for 'Changes in financial assets' and 'Changes in financial liabilities' are as per First Revised Estimates of 2021-22   .
-              2. Deposits with co-operative non-credit societies are included in bank deposits up to 1999-00. Since 2000-01, these deposits are included in non-banking  
-                  deposits.
-              3. Life Insurance Fund includes Central or State Governments employees' insurance funds and postal insurance funds.
-              4. Owing to changes in  coverage  of  non-banking deposits, data prior to 1997-98  are not strictly comparable with those of 1997-98 and onwards.
-              5. Shares and Debentures include investment in shares and debentures of credit / non-credit societies and investment in mutual funds  
-                 (other than Specified Undertaking of the UTI).
-              6. Since 2005-06, the data shown under 'Units of UTI' pertain to Administrator of the Specified Undertaking of the UTI. The UTI Mutual Fund is included in
-                  'Shares and Debentures'.
-              7. The sum of components of changes in financial assets do not add up to the total due to rounding off.                          
-              8. 'Bank advances' includes advances by scheduled commercial banks and co-operative banks &amp; societies.  
-              9. Loans and advances from other financial institutions' includes advances by non-banking finance companies, housing finance companies and insurance corporations.
-Also see Notes on Tables.
-Source : National Statistical Office (NSO).</t>
+    <t xml:space="preserve">Notes   :  1. Data for ‘Changes in financial assets’ and ‘Changes in financial liabilities’ are as per National Accounts Statistics 2025.
+               2. Deposits with co-operative non-credit societies are included in bank deposits up to 1999-00. Since 2000-01, these deposits are included
+                  in non-banking deposits.
+               3. Life Insurance Fund includes Central or State Governments employees’ insurance funds and postal insurance funds.
+               4. Owing to changes in coverage of non-banking deposits, data prior to 1997-98 are not strictly comparable with those of 1997-98 and
+                  onwards.
+               5. Shares and Debentures include investment in shares and debentures of credit / non-credit societies and investment in mutual funds
+                  (other than Specified Undertaking of the UTI).
+               6. Since 2005-06, the data shown under ‘Units of UTI’ pertain to Administrator of the Specified Undertaking of the UTI.
+                  The UTI Mutual Fund is included in ‘Shares and Debentures’.
+               7. The sum of components of changes in financial assets and financial liabilities may not add up to the total due to rounding off.
+               8. ‘Bank advances’ includes advances by scheduled commercial banks and co-operative banks &amp; societies.
+               9. Loans and advances from other financial institutions includes advances by non-banking finance companies, housing finance companies
+                  and insurance corporations.
+                  Also see Notes on Tables
+Source : National Statistics Office (NSO).</t>
   </si>
   <si>
     <t>Changes in Financial Assets/Liabilities of the Household Sector (At Current Prices)</t>
@@ -402,7 +407,7 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -420,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:Q65"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="15.4582386666667" customWidth="1"/>
@@ -428,12 +433,13 @@
     <col min="8" max="8" width="20.8542226666667" customWidth="1"/>
     <col min="9" max="9" width="20.839012" customWidth="1"/>
     <col min="10" max="17" width="20.8466173333333" customWidth="1"/>
+    <col min="18" max="18" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="15.999" customHeight="1">
       <c r="B2" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -445,7 +451,7 @@
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="13"/>
     </row>
@@ -555,49 +561,49 @@
         <v>16</v>
       </c>
       <c r="C8" s="7">
-        <v>118026</v>
+        <v>209451.37635</v>
       </c>
       <c r="D8" s="7">
-        <v>1.442142e6</v>
+        <v>1.184107203e6</v>
       </c>
       <c r="E8" s="7">
-        <v>-59126</v>
+        <v>55314.9094843868</v>
       </c>
       <c r="F8" s="7">
-        <v>589065</v>
+        <v>624639</v>
       </c>
       <c r="G8" s="7">
-        <v>719360</v>
+        <v>816988.049943011</v>
       </c>
       <c r="H8" s="7">
-        <v>336876</v>
+        <v>226402.78269734</v>
       </c>
       <c r="I8" s="7">
-        <v>276070</v>
+        <v>691333.671261951</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K8" s="7">
-        <v>8228</v>
+        <v>8040</v>
       </c>
       <c r="L8" s="7">
-        <v>3.43064e6</v>
+        <v>3.83121515462011e6</v>
       </c>
       <c r="M8" s="7">
-        <v>1.877458e6</v>
+        <v>1.23515892463201e6</v>
       </c>
       <c r="N8" s="7">
-        <v>1208</v>
+        <v>337878.220150492</v>
       </c>
       <c r="O8" s="7">
-        <v>334</v>
+        <v>576</v>
       </c>
       <c r="P8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q8" s="7">
-        <v>1.878999e6</v>
+        <v>1.5736131447825e6</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -605,49 +611,49 @@
         <v>18</v>
       </c>
       <c r="C9" s="8">
-        <v>237610</v>
+        <v>118247.97055</v>
       </c>
       <c r="D9" s="8">
-        <v>1.032971e6</v>
+        <v>1.4096518747e6</v>
       </c>
       <c r="E9" s="8">
-        <v>67275</v>
+        <v>-59126.4923854444</v>
       </c>
       <c r="F9" s="8">
-        <v>548944</v>
+        <v>642399</v>
       </c>
       <c r="G9" s="8">
-        <v>617793</v>
+        <v>723026.597157332</v>
       </c>
       <c r="H9" s="8">
-        <v>208140</v>
+        <v>335303.057</v>
       </c>
       <c r="I9" s="8">
-        <v>206241</v>
+        <v>358718.504335677</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K9" s="8">
-        <v>8629</v>
+        <v>8228</v>
       </c>
       <c r="L9" s="8">
-        <v>2.927604e6</v>
+        <v>3.60219851215919e6</v>
       </c>
       <c r="M9" s="8">
-        <v>1.252313e6</v>
+        <v>1.90718475289607e6</v>
       </c>
       <c r="N9" s="8">
-        <v>343354</v>
+        <v>1767.94710347313</v>
       </c>
       <c r="O9" s="8">
-        <v>818</v>
+        <v>334</v>
       </c>
       <c r="P9" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q9" s="8">
-        <v>1.596485e6</v>
+        <v>1.90928669999955e6</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -655,49 +661,49 @@
         <v>19</v>
       </c>
       <c r="C10" s="7">
-        <v>269667.3507</v>
+        <v>237609.720853793</v>
       </c>
       <c r="D10" s="7">
-        <v>783325.4816</v>
+        <v>992606.156760152</v>
       </c>
       <c r="E10" s="7">
-        <v>46321</v>
+        <v>67275.4789561911</v>
       </c>
       <c r="F10" s="7">
-        <v>486888.99</v>
+        <v>539753</v>
       </c>
       <c r="G10" s="7">
-        <v>551993.2091</v>
+        <v>618972.759006491</v>
       </c>
       <c r="H10" s="7">
-        <v>255357.2333</v>
+        <v>208140.3823136</v>
       </c>
       <c r="I10" s="7">
-        <v>214191.3206</v>
+        <v>260140.07178267</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K10" s="7">
-        <v>4229.22228</v>
+        <v>8629.2222789272</v>
       </c>
       <c r="L10" s="7">
-        <v>2.611973808e6</v>
+        <v>2.99198279156329e6</v>
       </c>
       <c r="M10" s="7">
-        <v>702351.0861</v>
+        <v>1.25626295848165e6</v>
       </c>
       <c r="N10" s="7">
-        <v>196639.736</v>
+        <v>343353.947251812</v>
       </c>
       <c r="O10" s="7">
-        <v>279.4136</v>
+        <v>818</v>
       </c>
       <c r="P10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q10" s="7">
-        <v>899270.2358</v>
+        <v>1.60043490573346e6</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -705,49 +711,49 @@
         <v>20</v>
       </c>
       <c r="C11" s="8">
-        <v>381976.0755</v>
+        <v>269667.3507</v>
       </c>
       <c r="D11" s="8">
-        <v>1.200657432e6</v>
+        <v>783325.4816</v>
       </c>
       <c r="E11" s="8">
-        <v>40724.20986</v>
+        <v>46321</v>
       </c>
       <c r="F11" s="8">
-        <v>569484.8282</v>
+        <v>486888.99</v>
       </c>
       <c r="G11" s="8">
-        <v>496387.3933</v>
+        <v>551993.2091</v>
       </c>
       <c r="H11" s="8">
-        <v>266384.3499</v>
+        <v>255357.2333</v>
       </c>
       <c r="I11" s="8">
-        <v>107184.3902</v>
+        <v>214191.3206</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K11" s="8">
-        <v>4222.12255</v>
+        <v>4229.22228</v>
       </c>
       <c r="L11" s="8">
-        <v>3.067020802e6</v>
+        <v>2.611973808e6</v>
       </c>
       <c r="M11" s="8">
-        <v>641272.4024</v>
+        <v>702351.0861</v>
       </c>
       <c r="N11" s="8">
-        <v>96679.21369</v>
+        <v>196639.736</v>
       </c>
       <c r="O11" s="8">
-        <v>-601.6867</v>
+        <v>279.4136</v>
       </c>
       <c r="P11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q11" s="8">
-        <v>737349.9294</v>
+        <v>899270.2358</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -755,49 +761,49 @@
         <v>21</v>
       </c>
       <c r="C12" s="7">
-        <v>282662</v>
+        <v>381976.0755</v>
       </c>
       <c r="D12" s="7">
-        <v>827901</v>
+        <v>1.200657432e6</v>
       </c>
       <c r="E12" s="7">
-        <v>56677</v>
+        <v>40724.20986</v>
       </c>
       <c r="F12" s="7">
-        <v>338572</v>
+        <v>569484.8282</v>
       </c>
       <c r="G12" s="7">
-        <v>452789</v>
+        <v>496387.3933</v>
       </c>
       <c r="H12" s="7">
-        <v>266963</v>
+        <v>266384.3499</v>
       </c>
       <c r="I12" s="7">
-        <v>94742</v>
+        <v>107184.3902</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="7">
-        <v>4257</v>
+        <v>4222.12255</v>
       </c>
       <c r="L12" s="7">
-        <v>2.324563e6</v>
+        <v>3.067020802e6</v>
       </c>
       <c r="M12" s="7">
-        <v>509958</v>
+        <v>641272.4024</v>
       </c>
       <c r="N12" s="7">
-        <v>264735</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>17</v>
+        <v>96679.21369</v>
+      </c>
+      <c r="O12" s="7">
+        <v>-601.6867</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q12" s="7">
-        <v>774693</v>
+        <v>737349.9294</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -805,49 +811,49 @@
         <v>22</v>
       </c>
       <c r="C13" s="8">
-        <v>277872</v>
+        <v>282662</v>
       </c>
       <c r="D13" s="8">
-        <v>777163</v>
+        <v>827901</v>
       </c>
       <c r="E13" s="8">
-        <v>33250</v>
+        <v>56677</v>
       </c>
       <c r="F13" s="8">
-        <v>387512</v>
+        <v>338572</v>
       </c>
       <c r="G13" s="8">
-        <v>404389</v>
+        <v>452789</v>
       </c>
       <c r="H13" s="8">
-        <v>206363</v>
+        <v>266963</v>
       </c>
       <c r="I13" s="8">
-        <v>172933</v>
+        <v>94742</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="8">
-        <v>4209</v>
+        <v>4257</v>
       </c>
       <c r="L13" s="8">
-        <v>2.26369e6</v>
+        <v>2.324563e6</v>
       </c>
       <c r="M13" s="8">
-        <v>604511</v>
+        <v>509958</v>
       </c>
       <c r="N13" s="8">
-        <v>166188</v>
-      </c>
-      <c r="O13" s="8">
-        <v>546</v>
+        <v>264735</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q13" s="8">
-        <v>771245</v>
+        <v>774693</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -855,49 +861,49 @@
         <v>23</v>
       </c>
       <c r="C14" s="7">
-        <v>484714</v>
+        <v>277872</v>
       </c>
       <c r="D14" s="7">
-        <v>521580</v>
+        <v>777163</v>
       </c>
       <c r="E14" s="7">
-        <v>-568</v>
+        <v>33250</v>
       </c>
       <c r="F14" s="7">
-        <v>343989</v>
+        <v>387512</v>
       </c>
       <c r="G14" s="7">
-        <v>369403</v>
+        <v>404389</v>
       </c>
       <c r="H14" s="7">
-        <v>155670</v>
+        <v>206363</v>
       </c>
       <c r="I14" s="7">
-        <v>177417</v>
+        <v>172933</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="7">
-        <v>4201</v>
+        <v>4209</v>
       </c>
       <c r="L14" s="7">
-        <v>2.056405e6</v>
+        <v>2.26369e6</v>
       </c>
       <c r="M14" s="7">
-        <v>525517</v>
+        <v>604511</v>
       </c>
       <c r="N14" s="7">
-        <v>224960</v>
+        <v>166188</v>
       </c>
       <c r="O14" s="7">
-        <v>222</v>
+        <v>546</v>
       </c>
       <c r="P14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q14" s="7">
-        <v>750700</v>
+        <v>771245</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -905,49 +911,49 @@
         <v>24</v>
       </c>
       <c r="C15" s="8">
-        <v>-332907</v>
+        <v>484714</v>
       </c>
       <c r="D15" s="8">
-        <v>938574</v>
+        <v>521580</v>
       </c>
       <c r="E15" s="8">
-        <v>34856</v>
+        <v>-568</v>
       </c>
       <c r="F15" s="8">
-        <v>354321</v>
+        <v>343989</v>
       </c>
       <c r="G15" s="8">
-        <v>325539</v>
+        <v>369403</v>
       </c>
       <c r="H15" s="8">
-        <v>115469</v>
+        <v>155670</v>
       </c>
       <c r="I15" s="8">
-        <v>174466</v>
+        <v>177417</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="8">
-        <v>4360</v>
+        <v>4201</v>
       </c>
       <c r="L15" s="8">
-        <v>1.614677e6</v>
+        <v>2.056405e6</v>
       </c>
       <c r="M15" s="8">
-        <v>345811</v>
+        <v>525517</v>
       </c>
       <c r="N15" s="8">
-        <v>122866</v>
+        <v>224960</v>
       </c>
       <c r="O15" s="8">
-        <v>-29</v>
+        <v>222</v>
       </c>
       <c r="P15" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q15" s="8">
-        <v>468648</v>
+        <v>750700</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -955,49 +961,49 @@
         <v>25</v>
       </c>
       <c r="C16" s="7">
-        <v>200518</v>
+        <v>-332907</v>
       </c>
       <c r="D16" s="7">
-        <v>622364</v>
+        <v>938574</v>
       </c>
       <c r="E16" s="7">
-        <v>18082</v>
+        <v>34856</v>
       </c>
       <c r="F16" s="7">
-        <v>264177</v>
+        <v>354321</v>
       </c>
       <c r="G16" s="7">
-        <v>290729</v>
+        <v>325539</v>
       </c>
       <c r="H16" s="7">
-        <v>67940</v>
+        <v>115469</v>
       </c>
       <c r="I16" s="7">
-        <v>28356</v>
+        <v>174466</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K16" s="7">
-        <v>4066</v>
+        <v>4360</v>
       </c>
       <c r="L16" s="7">
-        <v>1.496232e6</v>
+        <v>1.614677e6</v>
       </c>
       <c r="M16" s="7">
-        <v>269417</v>
+        <v>345811</v>
       </c>
       <c r="N16" s="7">
-        <v>115576</v>
+        <v>122866</v>
       </c>
       <c r="O16" s="7">
-        <v>395</v>
+        <v>-29</v>
       </c>
       <c r="P16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q16" s="7">
-        <v>385388</v>
+        <v>468648</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1005,49 +1011,49 @@
         <v>26</v>
       </c>
       <c r="C17" s="8">
-        <v>133345</v>
+        <v>200518</v>
       </c>
       <c r="D17" s="8">
-        <v>579272</v>
+        <v>622364</v>
       </c>
       <c r="E17" s="8">
-        <v>28915</v>
+        <v>18082</v>
       </c>
       <c r="F17" s="8">
-        <v>299322</v>
+        <v>264177</v>
       </c>
       <c r="G17" s="8">
-        <v>190883</v>
+        <v>290729</v>
       </c>
       <c r="H17" s="8">
-        <v>969</v>
+        <v>67940</v>
       </c>
       <c r="I17" s="8">
-        <v>20364</v>
+        <v>28356</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K17" s="8">
-        <v>4177</v>
+        <v>4066</v>
       </c>
       <c r="L17" s="8">
-        <v>1.257247e6</v>
+        <v>1.496232e6</v>
       </c>
       <c r="M17" s="8">
-        <v>282443</v>
+        <v>269417</v>
       </c>
       <c r="N17" s="8">
-        <v>94196</v>
+        <v>115576</v>
       </c>
       <c r="O17" s="8">
-        <v>193</v>
+        <v>395</v>
       </c>
       <c r="P17" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q17" s="8">
-        <v>376832</v>
+        <v>385388</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1055,49 +1061,49 @@
         <v>27</v>
       </c>
       <c r="C18" s="7">
-        <v>99520</v>
+        <v>133345</v>
       </c>
       <c r="D18" s="7">
-        <v>639304</v>
+        <v>579272</v>
       </c>
       <c r="E18" s="7">
-        <v>22816</v>
+        <v>28915</v>
       </c>
       <c r="F18" s="7">
-        <v>204469</v>
+        <v>299322</v>
       </c>
       <c r="G18" s="7">
-        <v>177841</v>
+        <v>190883</v>
       </c>
       <c r="H18" s="7">
-        <v>23053</v>
+        <v>969</v>
       </c>
       <c r="I18" s="7">
-        <v>18930</v>
+        <v>20364</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="7">
-        <v>4838</v>
+        <v>4177</v>
       </c>
       <c r="L18" s="7">
-        <v>1.19077e6</v>
+        <v>1.257247e6</v>
       </c>
       <c r="M18" s="7">
-        <v>302336</v>
+        <v>282443</v>
       </c>
       <c r="N18" s="7">
-        <v>55678</v>
+        <v>94196</v>
       </c>
       <c r="O18" s="7">
-        <v>665</v>
+        <v>193</v>
       </c>
       <c r="P18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q18" s="7">
-        <v>358679</v>
+        <v>376832</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1105,49 +1111,49 @@
         <v>28</v>
       </c>
       <c r="C19" s="8">
-        <v>111521</v>
+        <v>99520</v>
       </c>
       <c r="D19" s="8">
-        <v>575080</v>
+        <v>639304</v>
       </c>
       <c r="E19" s="8">
-        <v>27911</v>
+        <v>22816</v>
       </c>
       <c r="F19" s="8">
-        <v>179949</v>
+        <v>204469</v>
       </c>
       <c r="G19" s="8">
-        <v>156479</v>
+        <v>177841</v>
       </c>
       <c r="H19" s="8">
-        <v>-7109</v>
+        <v>23053</v>
       </c>
       <c r="I19" s="8">
-        <v>17027</v>
+        <v>18930</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="8">
-        <v>3183</v>
+        <v>4838</v>
       </c>
       <c r="L19" s="8">
-        <v>1.064041e6</v>
+        <v>1.19077e6</v>
       </c>
       <c r="M19" s="8">
-        <v>308747</v>
+        <v>302336</v>
       </c>
       <c r="N19" s="8">
-        <v>21510</v>
+        <v>55678</v>
       </c>
       <c r="O19" s="8">
-        <v>168</v>
+        <v>665</v>
       </c>
       <c r="P19" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q19" s="8">
-        <v>330425</v>
+        <v>358679</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1155,49 +1161,49 @@
         <v>29</v>
       </c>
       <c r="C20" s="7">
-        <v>106242</v>
+        <v>111521</v>
       </c>
       <c r="D20" s="7">
-        <v>525970</v>
+        <v>575080</v>
       </c>
       <c r="E20" s="7">
-        <v>10021</v>
+        <v>27911</v>
       </c>
       <c r="F20" s="7">
-        <v>195673</v>
+        <v>179949</v>
       </c>
       <c r="G20" s="7">
-        <v>95680</v>
+        <v>156479</v>
       </c>
       <c r="H20" s="7">
-        <v>-21889</v>
+        <v>-7109</v>
       </c>
       <c r="I20" s="7">
-        <v>16522</v>
+        <v>17027</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="7">
-        <v>4509</v>
+        <v>3183</v>
       </c>
       <c r="L20" s="7">
-        <v>932729</v>
+        <v>1.064041e6</v>
       </c>
       <c r="M20" s="7">
-        <v>272509</v>
+        <v>308747</v>
       </c>
       <c r="N20" s="7">
-        <v>17310</v>
+        <v>21510</v>
       </c>
       <c r="O20" s="7">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="P20" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Q20" s="7">
-        <v>290120</v>
+        <v>330425</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1205,49 +1211,49 @@
         <v>30</v>
       </c>
       <c r="C21" s="8">
-        <v>137131</v>
+        <v>106242</v>
       </c>
       <c r="D21" s="8">
-        <v>548299</v>
+        <v>525970</v>
       </c>
       <c r="E21" s="8">
-        <v>5099</v>
+        <v>10021</v>
       </c>
       <c r="F21" s="8">
-        <v>210102</v>
+        <v>195673</v>
       </c>
       <c r="G21" s="8">
-        <v>141139</v>
+        <v>95680</v>
       </c>
       <c r="H21" s="8">
-        <v>29545</v>
+        <v>-21889</v>
       </c>
       <c r="I21" s="8">
-        <v>1729</v>
+        <v>16522</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="8">
-        <v>6823</v>
+        <v>4509</v>
       </c>
       <c r="L21" s="8">
-        <v>1.079867e6</v>
+        <v>932729</v>
       </c>
       <c r="M21" s="8">
-        <v>269010</v>
+        <v>272509</v>
       </c>
       <c r="N21" s="8">
-        <v>8804</v>
+        <v>17310</v>
       </c>
       <c r="O21" s="8">
-        <v>-99</v>
-      </c>
-      <c r="P21" s="8">
-        <v>260</v>
+        <v>301</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="Q21" s="8">
-        <v>277975</v>
+        <v>290120</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1255,49 +1261,49 @@
         <v>31</v>
       </c>
       <c r="C22" s="7">
-        <v>96940</v>
+        <v>137131</v>
       </c>
       <c r="D22" s="7">
-        <v>398141</v>
+        <v>548299</v>
       </c>
       <c r="E22" s="7">
-        <v>18516</v>
+        <v>5099</v>
       </c>
       <c r="F22" s="7">
-        <v>259821</v>
+        <v>210102</v>
       </c>
       <c r="G22" s="7">
-        <v>129849</v>
+        <v>141139</v>
       </c>
       <c r="H22" s="7">
-        <v>43475</v>
+        <v>29545</v>
       </c>
       <c r="I22" s="7">
-        <v>44841</v>
+        <v>1729</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K22" s="7">
-        <v>-1784</v>
+        <v>6823</v>
       </c>
       <c r="L22" s="7">
-        <v>989798</v>
+        <v>1.079867e6</v>
       </c>
       <c r="M22" s="7">
-        <v>194443</v>
+        <v>269010</v>
       </c>
       <c r="N22" s="7">
-        <v>8899</v>
+        <v>8804</v>
       </c>
       <c r="O22" s="7">
-        <v>-147</v>
+        <v>-99</v>
       </c>
       <c r="P22" s="7">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Q22" s="7">
-        <v>203448</v>
+        <v>277975</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1305,49 +1311,49 @@
         <v>32</v>
       </c>
       <c r="C23" s="8">
-        <v>92188</v>
+        <v>96940</v>
       </c>
       <c r="D23" s="8">
-        <v>417833</v>
+        <v>398141</v>
       </c>
       <c r="E23" s="8">
-        <v>14742</v>
+        <v>18516</v>
       </c>
       <c r="F23" s="8">
-        <v>152861</v>
+        <v>259821</v>
       </c>
       <c r="G23" s="8">
-        <v>73398</v>
+        <v>129849</v>
       </c>
       <c r="H23" s="8">
-        <v>-27551</v>
+        <v>43475</v>
       </c>
       <c r="I23" s="8">
-        <v>-2333</v>
-      </c>
-      <c r="J23" s="8">
-        <v>-2737</v>
+        <v>44841</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="K23" s="8">
-        <v>8488</v>
+        <v>-1784</v>
       </c>
       <c r="L23" s="8">
-        <v>726889</v>
+        <v>989798</v>
       </c>
       <c r="M23" s="8">
-        <v>154735</v>
+        <v>194443</v>
       </c>
       <c r="N23" s="8">
-        <v>8812</v>
+        <v>8899</v>
       </c>
       <c r="O23" s="8">
-        <v>-199</v>
+        <v>-147</v>
       </c>
       <c r="P23" s="8">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q23" s="8">
-        <v>163598</v>
+        <v>203448</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1355,49 +1361,49 @@
         <v>33</v>
       </c>
       <c r="C24" s="7">
-        <v>81278</v>
+        <v>92188</v>
       </c>
       <c r="D24" s="7">
-        <v>389008</v>
+        <v>417833</v>
       </c>
       <c r="E24" s="7">
-        <v>1286</v>
+        <v>14742</v>
       </c>
       <c r="F24" s="7">
-        <v>169848</v>
+        <v>152861</v>
       </c>
       <c r="G24" s="7">
-        <v>71544</v>
+        <v>73398</v>
       </c>
       <c r="H24" s="7">
-        <v>-28327</v>
+        <v>-27551</v>
       </c>
       <c r="I24" s="7">
-        <v>74308</v>
+        <v>-2333</v>
       </c>
       <c r="J24" s="7">
-        <v>-324</v>
+        <v>-2737</v>
       </c>
       <c r="K24" s="7">
-        <v>13765</v>
+        <v>8488</v>
       </c>
       <c r="L24" s="7">
-        <v>772385</v>
+        <v>726889</v>
       </c>
       <c r="M24" s="7">
-        <v>179502</v>
+        <v>154735</v>
       </c>
       <c r="N24" s="7">
-        <v>8682</v>
+        <v>8812</v>
       </c>
       <c r="O24" s="7">
-        <v>-248</v>
+        <v>-199</v>
       </c>
       <c r="P24" s="7">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q24" s="7">
-        <v>188181</v>
+        <v>163598</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1405,49 +1411,49 @@
         <v>34</v>
       </c>
       <c r="C25" s="8">
-        <v>67194</v>
+        <v>81278</v>
       </c>
       <c r="D25" s="8">
-        <v>429282</v>
+        <v>389008</v>
       </c>
       <c r="E25" s="8">
-        <v>4584</v>
+        <v>1286</v>
       </c>
       <c r="F25" s="8">
-        <v>114851</v>
+        <v>169848</v>
       </c>
       <c r="G25" s="8">
-        <v>72503</v>
+        <v>71544</v>
       </c>
       <c r="H25" s="8">
-        <v>19198</v>
+        <v>-28327</v>
       </c>
       <c r="I25" s="8">
-        <v>50847</v>
+        <v>74308</v>
       </c>
       <c r="J25" s="8">
-        <v>-310</v>
+        <v>-324</v>
       </c>
       <c r="K25" s="8">
-        <v>6523</v>
+        <v>13765</v>
       </c>
       <c r="L25" s="8">
-        <v>764671</v>
+        <v>772385</v>
       </c>
       <c r="M25" s="8">
-        <v>273666</v>
+        <v>179502</v>
       </c>
       <c r="N25" s="8">
-        <v>9362</v>
+        <v>8682</v>
       </c>
       <c r="O25" s="8">
-        <v>-650</v>
+        <v>-248</v>
       </c>
       <c r="P25" s="8">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="Q25" s="8">
-        <v>282606</v>
+        <v>188181</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1455,49 +1461,49 @@
         <v>35</v>
       </c>
       <c r="C26" s="7">
-        <v>52151</v>
+        <v>67194</v>
       </c>
       <c r="D26" s="7">
-        <v>265716</v>
+        <v>429282</v>
       </c>
       <c r="E26" s="7">
-        <v>522</v>
+        <v>4584</v>
       </c>
       <c r="F26" s="7">
-        <v>83494</v>
+        <v>114851</v>
       </c>
       <c r="G26" s="7">
-        <v>61950</v>
+        <v>72503</v>
       </c>
       <c r="H26" s="7">
-        <v>87168</v>
+        <v>19198</v>
       </c>
       <c r="I26" s="7">
-        <v>33857</v>
+        <v>50847</v>
       </c>
       <c r="J26" s="7">
-        <v>-444</v>
+        <v>-310</v>
       </c>
       <c r="K26" s="7">
-        <v>-222</v>
+        <v>6523</v>
       </c>
       <c r="L26" s="7">
-        <v>584192</v>
+        <v>764671</v>
       </c>
       <c r="M26" s="7">
-        <v>175564</v>
+        <v>273666</v>
       </c>
       <c r="N26" s="7">
-        <v>8398</v>
+        <v>9362</v>
       </c>
       <c r="O26" s="7">
-        <v>-489</v>
+        <v>-650</v>
       </c>
       <c r="P26" s="7">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="Q26" s="7">
-        <v>183750</v>
+        <v>282606</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1505,49 +1511,49 @@
         <v>36</v>
       </c>
       <c r="C27" s="8">
-        <v>36977</v>
+        <v>52151</v>
       </c>
       <c r="D27" s="8">
-        <v>175045</v>
+        <v>265716</v>
       </c>
       <c r="E27" s="8">
-        <v>83</v>
+        <v>522</v>
       </c>
       <c r="F27" s="8">
-        <v>67986</v>
+        <v>83494</v>
       </c>
       <c r="G27" s="8">
-        <v>55794</v>
+        <v>61950</v>
       </c>
       <c r="H27" s="8">
-        <v>106420</v>
+        <v>87168</v>
       </c>
       <c r="I27" s="8">
-        <v>8113</v>
+        <v>33857</v>
       </c>
       <c r="J27" s="8">
-        <v>-3146</v>
+        <v>-444</v>
       </c>
       <c r="K27" s="8">
-        <v>-107</v>
+        <v>-222</v>
       </c>
       <c r="L27" s="8">
-        <v>447165</v>
+        <v>584192</v>
       </c>
       <c r="M27" s="8">
-        <v>111971</v>
+        <v>175564</v>
       </c>
       <c r="N27" s="8">
-        <v>8310</v>
+        <v>8398</v>
       </c>
       <c r="O27" s="8">
-        <v>-515</v>
+        <v>-489</v>
       </c>
       <c r="P27" s="8">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="Q27" s="8">
-        <v>120069</v>
+        <v>183750</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1555,49 +1561,49 @@
         <v>37</v>
       </c>
       <c r="C28" s="7">
-        <v>42675</v>
+        <v>36977</v>
       </c>
       <c r="D28" s="7">
-        <v>155934</v>
+        <v>175045</v>
       </c>
       <c r="E28" s="7">
-        <v>1945</v>
+        <v>83</v>
       </c>
       <c r="F28" s="7">
-        <v>52240</v>
+        <v>67986</v>
       </c>
       <c r="G28" s="7">
-        <v>48952</v>
+        <v>55794</v>
       </c>
       <c r="H28" s="7">
-        <v>87372</v>
+        <v>106420</v>
       </c>
       <c r="I28" s="7">
-        <v>9078</v>
+        <v>8113</v>
       </c>
       <c r="J28" s="7">
-        <v>-8586</v>
+        <v>-3146</v>
       </c>
       <c r="K28" s="7">
-        <v>-137</v>
+        <v>-107</v>
       </c>
       <c r="L28" s="7">
-        <v>389473</v>
+        <v>447165</v>
       </c>
       <c r="M28" s="7">
-        <v>57885</v>
+        <v>111971</v>
       </c>
       <c r="N28" s="7">
-        <v>12261</v>
+        <v>8310</v>
       </c>
       <c r="O28" s="7">
-        <v>-269</v>
+        <v>-515</v>
       </c>
       <c r="P28" s="7">
-        <v>105</v>
+        <v>304</v>
       </c>
       <c r="Q28" s="7">
-        <v>69982</v>
+        <v>120069</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1605,49 +1611,49 @@
         <v>38</v>
       </c>
       <c r="C29" s="8">
-        <v>28632</v>
+        <v>42675</v>
       </c>
       <c r="D29" s="8">
-        <v>122697</v>
+        <v>155934</v>
       </c>
       <c r="E29" s="8">
-        <v>12496</v>
+        <v>1945</v>
       </c>
       <c r="F29" s="8">
-        <v>52009</v>
+        <v>52240</v>
       </c>
       <c r="G29" s="8">
-        <v>45946</v>
+        <v>48952</v>
       </c>
       <c r="H29" s="8">
-        <v>56087</v>
+        <v>87372</v>
       </c>
       <c r="I29" s="8">
-        <v>7123</v>
+        <v>9078</v>
       </c>
       <c r="J29" s="8">
-        <v>-1618</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>17</v>
+        <v>-8586</v>
+      </c>
+      <c r="K29" s="8">
+        <v>-137</v>
       </c>
       <c r="L29" s="8">
-        <v>323372</v>
+        <v>389473</v>
       </c>
       <c r="M29" s="8">
-        <v>54388</v>
+        <v>57885</v>
       </c>
       <c r="N29" s="8">
-        <v>5247</v>
+        <v>12261</v>
       </c>
       <c r="O29" s="8">
-        <v>216</v>
+        <v>-269</v>
       </c>
       <c r="P29" s="8">
-        <v>423</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="8">
-        <v>60274</v>
+        <v>69982</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1655,49 +1661,49 @@
         <v>39</v>
       </c>
       <c r="C30" s="7">
-        <v>28156</v>
+        <v>28632</v>
       </c>
       <c r="D30" s="7">
-        <v>113033</v>
+        <v>122697</v>
       </c>
       <c r="E30" s="7">
-        <v>-347</v>
+        <v>12496</v>
       </c>
       <c r="F30" s="7">
-        <v>41237</v>
+        <v>52009</v>
       </c>
       <c r="G30" s="7">
-        <v>44223</v>
+        <v>45946</v>
       </c>
       <c r="H30" s="7">
-        <v>51938</v>
+        <v>56087</v>
       </c>
       <c r="I30" s="7">
-        <v>9834</v>
+        <v>7123</v>
       </c>
       <c r="J30" s="7">
-        <v>-1857</v>
-      </c>
-      <c r="K30" s="7">
-        <v>-183</v>
+        <v>-1618</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="L30" s="7">
-        <v>286034</v>
+        <v>323372</v>
       </c>
       <c r="M30" s="7">
-        <v>43354</v>
+        <v>54388</v>
       </c>
       <c r="N30" s="7">
-        <v>6878</v>
+        <v>5247</v>
       </c>
       <c r="O30" s="7">
-        <v>1111</v>
+        <v>216</v>
       </c>
       <c r="P30" s="7">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="Q30" s="7">
-        <v>51727</v>
+        <v>60274</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1705,49 +1711,49 @@
         <v>40</v>
       </c>
       <c r="C31" s="8">
-        <v>15632</v>
+        <v>28156</v>
       </c>
       <c r="D31" s="8">
-        <v>94709</v>
+        <v>113033</v>
       </c>
       <c r="E31" s="8">
-        <v>3004</v>
+        <v>-347</v>
       </c>
       <c r="F31" s="8">
-        <v>33861</v>
+        <v>41237</v>
       </c>
       <c r="G31" s="8">
-        <v>50863</v>
+        <v>44223</v>
       </c>
       <c r="H31" s="8">
-        <v>39007</v>
+        <v>51938</v>
       </c>
       <c r="I31" s="8">
-        <v>11148</v>
+        <v>9834</v>
       </c>
       <c r="J31" s="8">
-        <v>-934</v>
+        <v>-1857</v>
       </c>
       <c r="K31" s="8">
-        <v>183</v>
+        <v>-183</v>
       </c>
       <c r="L31" s="8">
-        <v>247475</v>
+        <v>286034</v>
       </c>
       <c r="M31" s="8">
-        <v>25439</v>
+        <v>43354</v>
       </c>
       <c r="N31" s="8">
-        <v>4741</v>
+        <v>6878</v>
       </c>
       <c r="O31" s="8">
-        <v>1319</v>
+        <v>1111</v>
       </c>
       <c r="P31" s="8">
-        <v>280</v>
+        <v>384</v>
       </c>
       <c r="Q31" s="8">
-        <v>31779</v>
+        <v>51727</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1755,49 +1761,49 @@
         <v>41</v>
       </c>
       <c r="C32" s="7">
-        <v>20845</v>
+        <v>15632</v>
       </c>
       <c r="D32" s="7">
-        <v>82892</v>
+        <v>94709</v>
       </c>
       <c r="E32" s="7">
-        <v>3844</v>
+        <v>3004</v>
       </c>
       <c r="F32" s="7">
-        <v>28644</v>
+        <v>33861</v>
       </c>
       <c r="G32" s="7">
-        <v>53907</v>
+        <v>50863</v>
       </c>
       <c r="H32" s="7">
-        <v>28985</v>
+        <v>39007</v>
       </c>
       <c r="I32" s="7">
-        <v>16308</v>
+        <v>11148</v>
       </c>
       <c r="J32" s="7">
-        <v>1811</v>
+        <v>-934</v>
       </c>
       <c r="K32" s="7">
-        <v>-1023</v>
+        <v>183</v>
       </c>
       <c r="L32" s="7">
-        <v>236213</v>
+        <v>247475</v>
       </c>
       <c r="M32" s="7">
-        <v>29859</v>
+        <v>25439</v>
       </c>
       <c r="N32" s="7">
-        <v>4631</v>
+        <v>4741</v>
       </c>
       <c r="O32" s="7">
-        <v>1227</v>
+        <v>1319</v>
       </c>
       <c r="P32" s="7">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="Q32" s="7">
-        <v>36067</v>
+        <v>31779</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1805,49 +1811,49 @@
         <v>42</v>
       </c>
       <c r="C33" s="8">
-        <v>21822</v>
+        <v>20845</v>
       </c>
       <c r="D33" s="8">
-        <v>79433</v>
+        <v>82892</v>
       </c>
       <c r="E33" s="8">
-        <v>7670</v>
+        <v>3844</v>
       </c>
       <c r="F33" s="8">
-        <v>23428</v>
+        <v>28644</v>
       </c>
       <c r="G33" s="8">
-        <v>46408</v>
+        <v>53907</v>
       </c>
       <c r="H33" s="8">
-        <v>28220</v>
+        <v>28985</v>
       </c>
       <c r="I33" s="8">
-        <v>5105</v>
+        <v>16308</v>
       </c>
       <c r="J33" s="8">
-        <v>1887</v>
+        <v>1811</v>
       </c>
       <c r="K33" s="8">
-        <v>-6870</v>
+        <v>-1023</v>
       </c>
       <c r="L33" s="8">
-        <v>207103</v>
+        <v>236213</v>
       </c>
       <c r="M33" s="8">
-        <v>20793</v>
+        <v>29859</v>
       </c>
       <c r="N33" s="8">
-        <v>4688</v>
+        <v>4631</v>
       </c>
       <c r="O33" s="8">
-        <v>944</v>
+        <v>1227</v>
       </c>
       <c r="P33" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q33" s="8">
-        <v>26773</v>
+        <v>36067</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1855,49 +1861,49 @@
         <v>43</v>
       </c>
       <c r="C34" s="7">
-        <v>12780</v>
+        <v>21822</v>
       </c>
       <c r="D34" s="7">
-        <v>74099</v>
+        <v>79433</v>
       </c>
       <c r="E34" s="7">
-        <v>6733</v>
+        <v>7670</v>
       </c>
       <c r="F34" s="7">
-        <v>19410</v>
+        <v>23428</v>
       </c>
       <c r="G34" s="7">
-        <v>32267</v>
+        <v>46408</v>
       </c>
       <c r="H34" s="7">
-        <v>22162</v>
+        <v>28220</v>
       </c>
       <c r="I34" s="7">
-        <v>4464</v>
+        <v>5105</v>
       </c>
       <c r="J34" s="7">
-        <v>595</v>
+        <v>1887</v>
       </c>
       <c r="K34" s="7">
-        <v>-770</v>
+        <v>-6870</v>
       </c>
       <c r="L34" s="7">
-        <v>171740</v>
+        <v>207103</v>
       </c>
       <c r="M34" s="7">
-        <v>19885</v>
+        <v>20793</v>
       </c>
       <c r="N34" s="7">
-        <v>4203</v>
+        <v>4688</v>
       </c>
       <c r="O34" s="7">
-        <v>488</v>
+        <v>944</v>
       </c>
       <c r="P34" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q34" s="7">
-        <v>24919</v>
+        <v>26773</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1905,49 +1911,49 @@
         <v>44</v>
       </c>
       <c r="C35" s="8">
-        <v>13643</v>
+        <v>12780</v>
       </c>
       <c r="D35" s="8">
-        <v>50902</v>
+        <v>74099</v>
       </c>
       <c r="E35" s="8">
-        <v>25980</v>
+        <v>6733</v>
       </c>
       <c r="F35" s="8">
-        <v>16121</v>
+        <v>19410</v>
       </c>
       <c r="G35" s="8">
-        <v>30390</v>
+        <v>32267</v>
       </c>
       <c r="H35" s="8">
-        <v>11783</v>
+        <v>22162</v>
       </c>
       <c r="I35" s="8">
-        <v>6631</v>
+        <v>4464</v>
       </c>
       <c r="J35" s="8">
-        <v>3776</v>
+        <v>595</v>
       </c>
       <c r="K35" s="8">
-        <v>-708</v>
+        <v>-770</v>
       </c>
       <c r="L35" s="8">
-        <v>158519</v>
+        <v>171740</v>
       </c>
       <c r="M35" s="8">
-        <v>13675</v>
+        <v>19885</v>
       </c>
       <c r="N35" s="8">
-        <v>2593</v>
+        <v>4203</v>
       </c>
       <c r="O35" s="8">
-        <v>229</v>
+        <v>488</v>
       </c>
       <c r="P35" s="8">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="Q35" s="8">
-        <v>16857</v>
+        <v>24919</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -1955,49 +1961,49 @@
         <v>45</v>
       </c>
       <c r="C36" s="7">
-        <v>16525</v>
+        <v>13643</v>
       </c>
       <c r="D36" s="7">
-        <v>39941</v>
+        <v>50902</v>
       </c>
       <c r="E36" s="7">
-        <v>13198</v>
+        <v>25980</v>
       </c>
       <c r="F36" s="7">
-        <v>13894</v>
+        <v>16121</v>
       </c>
       <c r="G36" s="7">
-        <v>22343</v>
+        <v>30390</v>
       </c>
       <c r="H36" s="7">
-        <v>9588</v>
+        <v>11783</v>
       </c>
       <c r="I36" s="7">
-        <v>8839</v>
+        <v>6631</v>
       </c>
       <c r="J36" s="7">
-        <v>262</v>
+        <v>3776</v>
       </c>
       <c r="K36" s="7">
-        <v>-252</v>
+        <v>-708</v>
       </c>
       <c r="L36" s="7">
-        <v>124337</v>
+        <v>158519</v>
       </c>
       <c r="M36" s="7">
-        <v>15605</v>
+        <v>13675</v>
       </c>
       <c r="N36" s="7">
-        <v>2398</v>
+        <v>2593</v>
       </c>
       <c r="O36" s="7">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="P36" s="7">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="Q36" s="7">
-        <v>18620</v>
+        <v>16857</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2005,49 +2011,49 @@
         <v>46</v>
       </c>
       <c r="C37" s="8">
-        <v>15916</v>
+        <v>16525</v>
       </c>
       <c r="D37" s="8">
-        <v>55835</v>
+        <v>39941</v>
       </c>
       <c r="E37" s="8">
-        <v>11547</v>
+        <v>13198</v>
       </c>
       <c r="F37" s="8">
-        <v>11370</v>
+        <v>13894</v>
       </c>
       <c r="G37" s="8">
-        <v>21414</v>
+        <v>22343</v>
       </c>
       <c r="H37" s="8">
-        <v>13186</v>
+        <v>9588</v>
       </c>
       <c r="I37" s="8">
-        <v>13473</v>
+        <v>8839</v>
       </c>
       <c r="J37" s="8">
-        <v>3908</v>
+        <v>262</v>
       </c>
       <c r="K37" s="8">
-        <v>-1148</v>
+        <v>-252</v>
       </c>
       <c r="L37" s="8">
-        <v>145501</v>
+        <v>124337</v>
       </c>
       <c r="M37" s="8">
-        <v>21618</v>
+        <v>15605</v>
       </c>
       <c r="N37" s="8">
-        <v>2409</v>
+        <v>2398</v>
       </c>
       <c r="O37" s="8">
-        <v>417</v>
+        <v>275</v>
       </c>
       <c r="P37" s="8">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="Q37" s="8">
-        <v>24770</v>
+        <v>18620</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2055,49 +2061,49 @@
         <v>47</v>
       </c>
       <c r="C38" s="7">
-        <v>13367</v>
+        <v>15916</v>
       </c>
       <c r="D38" s="7">
-        <v>36236</v>
+        <v>55835</v>
       </c>
       <c r="E38" s="7">
-        <v>11654</v>
+        <v>11547</v>
       </c>
       <c r="F38" s="7">
-        <v>9548</v>
+        <v>11370</v>
       </c>
       <c r="G38" s="7">
-        <v>18323</v>
+        <v>21414</v>
       </c>
       <c r="H38" s="7">
-        <v>6908</v>
+        <v>13186</v>
       </c>
       <c r="I38" s="7">
-        <v>10067</v>
+        <v>13473</v>
       </c>
       <c r="J38" s="7">
-        <v>4705</v>
+        <v>3908</v>
       </c>
       <c r="K38" s="7">
-        <v>-1190</v>
+        <v>-1148</v>
       </c>
       <c r="L38" s="7">
-        <v>109618</v>
+        <v>145501</v>
       </c>
       <c r="M38" s="7">
-        <v>11972</v>
+        <v>21618</v>
       </c>
       <c r="N38" s="7">
-        <v>1867</v>
+        <v>2409</v>
       </c>
       <c r="O38" s="7">
-        <v>710</v>
+        <v>417</v>
       </c>
       <c r="P38" s="7">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="Q38" s="7">
-        <v>14859</v>
+        <v>24770</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2105,49 +2111,49 @@
         <v>48</v>
       </c>
       <c r="C39" s="8">
-        <v>6562</v>
+        <v>13367</v>
       </c>
       <c r="D39" s="8">
-        <v>29518</v>
+        <v>36236</v>
       </c>
       <c r="E39" s="8">
-        <v>6035</v>
+        <v>11654</v>
       </c>
       <c r="F39" s="8">
-        <v>7114</v>
+        <v>9548</v>
       </c>
       <c r="G39" s="8">
-        <v>14814</v>
+        <v>18323</v>
       </c>
       <c r="H39" s="8">
-        <v>3885</v>
+        <v>6908</v>
       </c>
       <c r="I39" s="8">
-        <v>8212</v>
+        <v>10067</v>
       </c>
       <c r="J39" s="8">
-        <v>5612</v>
+        <v>4705</v>
       </c>
       <c r="K39" s="8">
-        <v>-1398</v>
+        <v>-1190</v>
       </c>
       <c r="L39" s="8">
-        <v>80354</v>
+        <v>109618</v>
       </c>
       <c r="M39" s="8">
-        <v>11421</v>
+        <v>11972</v>
       </c>
       <c r="N39" s="8">
-        <v>2897</v>
+        <v>1867</v>
       </c>
       <c r="O39" s="8">
-        <v>443</v>
+        <v>710</v>
       </c>
       <c r="P39" s="8">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="Q39" s="8">
-        <v>15056</v>
+        <v>14859</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2155,49 +2161,49 @@
         <v>49</v>
       </c>
       <c r="C40" s="7">
-        <v>8157</v>
+        <v>6562</v>
       </c>
       <c r="D40" s="7">
-        <v>17848</v>
+        <v>29518</v>
       </c>
       <c r="E40" s="7">
-        <v>2218</v>
+        <v>6035</v>
       </c>
       <c r="F40" s="7">
-        <v>7003</v>
+        <v>7114</v>
       </c>
       <c r="G40" s="7">
-        <v>12501</v>
+        <v>14814</v>
       </c>
       <c r="H40" s="7">
-        <v>4845</v>
+        <v>3885</v>
       </c>
       <c r="I40" s="7">
-        <v>6800</v>
+        <v>8212</v>
       </c>
       <c r="J40" s="7">
-        <v>9087</v>
+        <v>5612</v>
       </c>
       <c r="K40" s="7">
-        <v>-414</v>
+        <v>-1398</v>
       </c>
       <c r="L40" s="7">
-        <v>68045</v>
+        <v>80354</v>
       </c>
       <c r="M40" s="7">
-        <v>3689</v>
+        <v>11421</v>
       </c>
       <c r="N40" s="7">
-        <v>1551</v>
+        <v>2897</v>
       </c>
       <c r="O40" s="7">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="P40" s="7">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="Q40" s="7">
-        <v>5997</v>
+        <v>15056</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2205,49 +2211,49 @@
         <v>50</v>
       </c>
       <c r="C41" s="8">
-        <v>6251</v>
+        <v>8157</v>
       </c>
       <c r="D41" s="8">
-        <v>18777</v>
+        <v>17848</v>
       </c>
       <c r="E41" s="8">
-        <v>1286</v>
+        <v>2218</v>
       </c>
       <c r="F41" s="8">
-        <v>5599</v>
+        <v>7003</v>
       </c>
       <c r="G41" s="8">
-        <v>11155</v>
+        <v>12501</v>
       </c>
       <c r="H41" s="8">
-        <v>7883</v>
+        <v>4845</v>
       </c>
       <c r="I41" s="8">
-        <v>4972</v>
+        <v>6800</v>
       </c>
       <c r="J41" s="8">
-        <v>3438</v>
+        <v>9087</v>
       </c>
       <c r="K41" s="8">
-        <v>-453</v>
+        <v>-414</v>
       </c>
       <c r="L41" s="8">
-        <v>58908</v>
+        <v>68045</v>
       </c>
       <c r="M41" s="8">
-        <v>7429</v>
+        <v>3689</v>
       </c>
       <c r="N41" s="8">
-        <v>1154</v>
+        <v>1551</v>
       </c>
       <c r="O41" s="8">
-        <v>611</v>
+        <v>469</v>
       </c>
       <c r="P41" s="8">
-        <v>73</v>
+        <v>288</v>
       </c>
       <c r="Q41" s="8">
-        <v>9267</v>
+        <v>5997</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2255,49 +2261,49 @@
         <v>51</v>
       </c>
       <c r="C42" s="7">
-        <v>7655</v>
+        <v>6251</v>
       </c>
       <c r="D42" s="7">
-        <v>13987</v>
+        <v>18777</v>
       </c>
       <c r="E42" s="7">
-        <v>1839</v>
+        <v>1286</v>
       </c>
       <c r="F42" s="7">
-        <v>4415</v>
+        <v>5599</v>
       </c>
       <c r="G42" s="7">
-        <v>9508</v>
+        <v>11155</v>
       </c>
       <c r="H42" s="7">
-        <v>6758</v>
+        <v>7883</v>
       </c>
       <c r="I42" s="7">
-        <v>2655</v>
+        <v>4972</v>
       </c>
       <c r="J42" s="7">
-        <v>2179</v>
+        <v>3438</v>
       </c>
       <c r="K42" s="7">
-        <v>-763</v>
+        <v>-453</v>
       </c>
       <c r="L42" s="7">
-        <v>48233</v>
+        <v>58908</v>
       </c>
       <c r="M42" s="7">
-        <v>8303</v>
+        <v>7429</v>
       </c>
       <c r="N42" s="7">
-        <v>1053</v>
+        <v>1154</v>
       </c>
       <c r="O42" s="7">
-        <v>747</v>
+        <v>611</v>
       </c>
       <c r="P42" s="7">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="Q42" s="7">
-        <v>10188</v>
+        <v>9267</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2305,49 +2311,49 @@
         <v>52</v>
       </c>
       <c r="C43" s="8">
-        <v>4256</v>
+        <v>7655</v>
       </c>
       <c r="D43" s="8">
-        <v>14747</v>
+        <v>13987</v>
       </c>
       <c r="E43" s="8">
-        <v>1580</v>
+        <v>1839</v>
       </c>
       <c r="F43" s="8">
-        <v>3423</v>
+        <v>4415</v>
       </c>
       <c r="G43" s="8">
-        <v>7552</v>
+        <v>9508</v>
       </c>
       <c r="H43" s="8">
-        <v>5478</v>
+        <v>6758</v>
       </c>
       <c r="I43" s="8">
-        <v>1136</v>
+        <v>2655</v>
       </c>
       <c r="J43" s="8">
-        <v>1427</v>
+        <v>2179</v>
       </c>
       <c r="K43" s="8">
-        <v>359</v>
+        <v>-763</v>
       </c>
       <c r="L43" s="8">
-        <v>39958</v>
+        <v>48233</v>
       </c>
       <c r="M43" s="8">
-        <v>11436</v>
+        <v>8303</v>
       </c>
       <c r="N43" s="8">
-        <v>713</v>
+        <v>1053</v>
       </c>
       <c r="O43" s="8">
-        <v>474</v>
+        <v>747</v>
       </c>
       <c r="P43" s="8">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="Q43" s="8">
-        <v>12826</v>
+        <v>10188</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2355,49 +2361,49 @@
         <v>53</v>
       </c>
       <c r="C44" s="7">
-        <v>4815</v>
+        <v>4256</v>
       </c>
       <c r="D44" s="7">
-        <v>14674</v>
+        <v>14747</v>
       </c>
       <c r="E44" s="7">
-        <v>1326</v>
+        <v>1580</v>
       </c>
       <c r="F44" s="7">
-        <v>2589</v>
+        <v>3423</v>
       </c>
       <c r="G44" s="7">
-        <v>6509</v>
+        <v>7552</v>
       </c>
       <c r="H44" s="7">
-        <v>3680</v>
+        <v>5478</v>
       </c>
       <c r="I44" s="7">
-        <v>813</v>
+        <v>1136</v>
       </c>
       <c r="J44" s="7">
-        <v>1196</v>
+        <v>1427</v>
       </c>
       <c r="K44" s="7">
-        <v>504</v>
+        <v>359</v>
       </c>
       <c r="L44" s="7">
-        <v>36106</v>
+        <v>39958</v>
       </c>
       <c r="M44" s="7">
-        <v>8159</v>
+        <v>11436</v>
       </c>
       <c r="N44" s="7">
-        <v>555</v>
+        <v>713</v>
       </c>
       <c r="O44" s="7">
-        <v>347</v>
+        <v>474</v>
       </c>
       <c r="P44" s="7">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="Q44" s="7">
-        <v>9287</v>
+        <v>12826</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2405,49 +2411,49 @@
         <v>54</v>
       </c>
       <c r="C45" s="8">
-        <v>3090</v>
+        <v>4815</v>
       </c>
       <c r="D45" s="8">
-        <v>14510</v>
+        <v>14674</v>
       </c>
       <c r="E45" s="8">
-        <v>1512</v>
+        <v>1326</v>
       </c>
       <c r="F45" s="8">
-        <v>2159</v>
+        <v>2589</v>
       </c>
       <c r="G45" s="8">
-        <v>5055</v>
+        <v>6509</v>
       </c>
       <c r="H45" s="8">
-        <v>3092</v>
+        <v>3680</v>
       </c>
       <c r="I45" s="8">
-        <v>1768</v>
+        <v>813</v>
       </c>
       <c r="J45" s="8">
-        <v>943</v>
+        <v>1196</v>
       </c>
       <c r="K45" s="8">
-        <v>-280</v>
+        <v>504</v>
       </c>
       <c r="L45" s="8">
-        <v>31849</v>
+        <v>36106</v>
       </c>
       <c r="M45" s="8">
-        <v>7345</v>
+        <v>8159</v>
       </c>
       <c r="N45" s="8">
-        <v>522</v>
+        <v>555</v>
       </c>
       <c r="O45" s="8">
-        <v>435</v>
+        <v>347</v>
       </c>
       <c r="P45" s="8">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="Q45" s="8">
-        <v>8510</v>
+        <v>9287</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2455,49 +2461,49 @@
         <v>55</v>
       </c>
       <c r="C46" s="7">
-        <v>2220</v>
+        <v>3090</v>
       </c>
       <c r="D46" s="7">
-        <v>10603</v>
+        <v>14510</v>
       </c>
       <c r="E46" s="7">
-        <v>1423</v>
+        <v>1512</v>
       </c>
       <c r="F46" s="7">
-        <v>1779</v>
+        <v>2159</v>
       </c>
       <c r="G46" s="7">
-        <v>4188</v>
+        <v>5055</v>
       </c>
       <c r="H46" s="7">
-        <v>3413</v>
+        <v>3092</v>
       </c>
       <c r="I46" s="7">
-        <v>1394</v>
+        <v>1768</v>
       </c>
       <c r="J46" s="7">
-        <v>586</v>
+        <v>943</v>
       </c>
       <c r="K46" s="7">
-        <v>-44</v>
+        <v>-280</v>
       </c>
       <c r="L46" s="7">
-        <v>25562</v>
+        <v>31849</v>
       </c>
       <c r="M46" s="7">
-        <v>6043</v>
+        <v>7345</v>
       </c>
       <c r="N46" s="7">
-        <v>646</v>
+        <v>522</v>
       </c>
       <c r="O46" s="7">
-        <v>205</v>
+        <v>435</v>
       </c>
       <c r="P46" s="7">
-        <v>89</v>
+        <v>208</v>
       </c>
       <c r="Q46" s="7">
-        <v>6983</v>
+        <v>8510</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2505,49 +2511,49 @@
         <v>56</v>
       </c>
       <c r="C47" s="8">
-        <v>2938</v>
+        <v>2220</v>
       </c>
       <c r="D47" s="8">
-        <v>9859</v>
+        <v>10603</v>
       </c>
       <c r="E47" s="8">
-        <v>960</v>
+        <v>1423</v>
       </c>
       <c r="F47" s="8">
-        <v>1556</v>
+        <v>1779</v>
       </c>
       <c r="G47" s="8">
-        <v>3759</v>
+        <v>4188</v>
       </c>
       <c r="H47" s="8">
-        <v>3107</v>
+        <v>3413</v>
       </c>
       <c r="I47" s="8">
-        <v>762</v>
+        <v>1394</v>
       </c>
       <c r="J47" s="8">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="K47" s="8">
-        <v>41</v>
+        <v>-44</v>
       </c>
       <c r="L47" s="8">
-        <v>23549</v>
+        <v>25562</v>
       </c>
       <c r="M47" s="8">
-        <v>5002</v>
+        <v>6043</v>
       </c>
       <c r="N47" s="8">
-        <v>420</v>
+        <v>646</v>
       </c>
       <c r="O47" s="8">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="P47" s="8">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="Q47" s="8">
-        <v>5733</v>
+        <v>6983</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2555,49 +2561,49 @@
         <v>57</v>
       </c>
       <c r="C48" s="7">
-        <v>2776</v>
+        <v>2938</v>
       </c>
       <c r="D48" s="7">
-        <v>7978</v>
+        <v>9859</v>
       </c>
       <c r="E48" s="7">
-        <v>1019</v>
+        <v>960</v>
       </c>
       <c r="F48" s="7">
-        <v>1376</v>
+        <v>1556</v>
       </c>
       <c r="G48" s="7">
-        <v>3052</v>
+        <v>3759</v>
       </c>
       <c r="H48" s="7">
-        <v>1976</v>
+        <v>3107</v>
       </c>
       <c r="I48" s="7">
-        <v>555</v>
+        <v>762</v>
       </c>
       <c r="J48" s="7">
-        <v>222</v>
+        <v>567</v>
       </c>
       <c r="K48" s="7">
-        <v>-164</v>
+        <v>41</v>
       </c>
       <c r="L48" s="7">
-        <v>18790</v>
+        <v>23549</v>
       </c>
       <c r="M48" s="7">
-        <v>4469</v>
+        <v>5002</v>
       </c>
       <c r="N48" s="7">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="O48" s="7">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="P48" s="7">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="Q48" s="7">
-        <v>5238</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2605,49 +2611,49 @@
         <v>58</v>
       </c>
       <c r="C49" s="8">
-        <v>2026</v>
+        <v>2776</v>
       </c>
       <c r="D49" s="8">
-        <v>6661</v>
+        <v>7978</v>
       </c>
       <c r="E49" s="8">
-        <v>870</v>
+        <v>1019</v>
       </c>
       <c r="F49" s="8">
-        <v>1235</v>
+        <v>1376</v>
       </c>
       <c r="G49" s="8">
-        <v>2865</v>
+        <v>3052</v>
       </c>
       <c r="H49" s="8">
-        <v>1243</v>
+        <v>1976</v>
       </c>
       <c r="I49" s="8">
-        <v>646</v>
+        <v>555</v>
       </c>
       <c r="J49" s="8">
-        <v>122</v>
+        <v>222</v>
       </c>
       <c r="K49" s="8">
-        <v>429</v>
+        <v>-164</v>
       </c>
       <c r="L49" s="8">
-        <v>16097</v>
+        <v>18790</v>
       </c>
       <c r="M49" s="8">
-        <v>2946</v>
+        <v>4469</v>
       </c>
       <c r="N49" s="8">
-        <v>349</v>
+        <v>460</v>
       </c>
       <c r="O49" s="8">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="P49" s="8">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q49" s="8">
-        <v>3531</v>
+        <v>5238</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2655,49 +2661,49 @@
         <v>59</v>
       </c>
       <c r="C50" s="7">
-        <v>965</v>
+        <v>2026</v>
       </c>
       <c r="D50" s="7">
-        <v>5194</v>
+        <v>6661</v>
       </c>
       <c r="E50" s="7">
-        <v>894</v>
+        <v>870</v>
       </c>
       <c r="F50" s="7">
-        <v>1037</v>
+        <v>1235</v>
       </c>
       <c r="G50" s="7">
-        <v>2480</v>
+        <v>2865</v>
       </c>
       <c r="H50" s="7">
-        <v>1784</v>
+        <v>1243</v>
       </c>
       <c r="I50" s="7">
-        <v>510</v>
+        <v>646</v>
       </c>
       <c r="J50" s="7">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K50" s="7">
-        <v>643</v>
+        <v>429</v>
       </c>
       <c r="L50" s="7">
-        <v>13621</v>
+        <v>16097</v>
       </c>
       <c r="M50" s="7">
-        <v>3507</v>
+        <v>2946</v>
       </c>
       <c r="N50" s="7">
-        <v>244</v>
+        <v>349</v>
       </c>
       <c r="O50" s="7">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="P50" s="7">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="Q50" s="7">
-        <v>4033</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2705,49 +2711,49 @@
         <v>60</v>
       </c>
       <c r="C51" s="8">
-        <v>1625</v>
+        <v>965</v>
       </c>
       <c r="D51" s="8">
-        <v>5550</v>
+        <v>5194</v>
       </c>
       <c r="E51" s="8">
-        <v>378</v>
+        <v>894</v>
       </c>
       <c r="F51" s="8">
-        <v>915</v>
+        <v>1037</v>
       </c>
       <c r="G51" s="8">
-        <v>2122</v>
+        <v>2480</v>
       </c>
       <c r="H51" s="8">
-        <v>712</v>
+        <v>1784</v>
       </c>
       <c r="I51" s="8">
-        <v>412</v>
+        <v>510</v>
       </c>
       <c r="J51" s="8">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="K51" s="8">
-        <v>373</v>
+        <v>643</v>
       </c>
       <c r="L51" s="8">
-        <v>12118</v>
+        <v>13621</v>
       </c>
       <c r="M51" s="8">
-        <v>3093</v>
+        <v>3507</v>
       </c>
       <c r="N51" s="8">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="O51" s="8">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P51" s="8">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="Q51" s="8">
-        <v>3508</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2755,49 +2761,49 @@
         <v>61</v>
       </c>
       <c r="C52" s="7">
-        <v>1332</v>
+        <v>1625</v>
       </c>
       <c r="D52" s="7">
-        <v>4659</v>
+        <v>5550</v>
       </c>
       <c r="E52" s="7">
-        <v>477</v>
+        <v>378</v>
       </c>
       <c r="F52" s="7">
-        <v>773</v>
+        <v>915</v>
       </c>
       <c r="G52" s="7">
-        <v>1748</v>
+        <v>2122</v>
       </c>
       <c r="H52" s="7">
-        <v>531</v>
+        <v>712</v>
       </c>
       <c r="I52" s="7">
-        <v>253</v>
+        <v>412</v>
       </c>
       <c r="J52" s="7">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K52" s="7">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="L52" s="7">
-        <v>10249</v>
+        <v>12118</v>
       </c>
       <c r="M52" s="7">
-        <v>2868</v>
+        <v>3093</v>
       </c>
       <c r="N52" s="7">
-        <v>393</v>
+        <v>182</v>
       </c>
       <c r="O52" s="7">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="P52" s="7">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="Q52" s="7">
-        <v>3551</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2805,49 +2811,49 @@
         <v>62</v>
       </c>
       <c r="C53" s="8">
-        <v>1430</v>
+        <v>1332</v>
       </c>
       <c r="D53" s="8">
-        <v>4626</v>
+        <v>4659</v>
       </c>
       <c r="E53" s="8">
-        <v>232</v>
+        <v>477</v>
       </c>
       <c r="F53" s="8">
-        <v>683</v>
+        <v>773</v>
       </c>
       <c r="G53" s="8">
-        <v>1605</v>
+        <v>1748</v>
       </c>
       <c r="H53" s="8">
-        <v>227</v>
+        <v>531</v>
       </c>
       <c r="I53" s="8">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="J53" s="8">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="K53" s="8">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L53" s="8">
-        <v>9483</v>
+        <v>10249</v>
       </c>
       <c r="M53" s="8">
-        <v>2125</v>
+        <v>2868</v>
       </c>
       <c r="N53" s="8">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="O53" s="8">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="P53" s="8">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="Q53" s="8">
-        <v>2738</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2855,49 +2861,49 @@
         <v>63</v>
       </c>
       <c r="C54" s="7">
-        <v>703</v>
+        <v>1430</v>
       </c>
       <c r="D54" s="7">
-        <v>3521</v>
+        <v>4626</v>
       </c>
       <c r="E54" s="7">
+        <v>232</v>
+      </c>
+      <c r="F54" s="7">
+        <v>683</v>
+      </c>
+      <c r="G54" s="7">
+        <v>1605</v>
+      </c>
+      <c r="H54" s="7">
         <v>227</v>
       </c>
-      <c r="F54" s="7">
-        <v>592</v>
-      </c>
-      <c r="G54" s="7">
-        <v>1316</v>
-      </c>
-      <c r="H54" s="7">
-        <v>325</v>
-      </c>
       <c r="I54" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J54" s="7">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="K54" s="7">
-        <v>235</v>
+        <v>397</v>
       </c>
       <c r="L54" s="7">
-        <v>7154</v>
+        <v>9483</v>
       </c>
       <c r="M54" s="7">
-        <v>1481</v>
+        <v>2125</v>
       </c>
       <c r="N54" s="7">
-        <v>125</v>
+        <v>352</v>
       </c>
       <c r="O54" s="7">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="P54" s="7">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="Q54" s="7">
-        <v>1711</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2905,49 +2911,49 @@
         <v>64</v>
       </c>
       <c r="C55" s="8">
-        <v>1140</v>
+        <v>703</v>
       </c>
       <c r="D55" s="8">
-        <v>3920</v>
+        <v>3521</v>
       </c>
       <c r="E55" s="8">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c r="F55" s="8">
-        <v>524</v>
+        <v>592</v>
       </c>
       <c r="G55" s="8">
-        <v>1172</v>
+        <v>1316</v>
       </c>
       <c r="H55" s="8">
-        <v>19</v>
+        <v>325</v>
       </c>
       <c r="I55" s="8">
-        <v>-5</v>
+        <v>201</v>
       </c>
       <c r="J55" s="8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K55" s="8">
-        <v>-253</v>
+        <v>235</v>
       </c>
       <c r="L55" s="8">
-        <v>6651</v>
+        <v>7154</v>
       </c>
       <c r="M55" s="8">
-        <v>1232</v>
+        <v>1481</v>
       </c>
       <c r="N55" s="8">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="O55" s="8">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="P55" s="8">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="Q55" s="8">
-        <v>1456</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2955,49 +2961,49 @@
         <v>65</v>
       </c>
       <c r="C56" s="7">
-        <v>342</v>
+        <v>1140</v>
       </c>
       <c r="D56" s="7">
-        <v>2120</v>
+        <v>3920</v>
       </c>
       <c r="E56" s="7">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="F56" s="7">
-        <v>423</v>
+        <v>524</v>
       </c>
       <c r="G56" s="7">
-        <v>1224</v>
+        <v>1172</v>
       </c>
       <c r="H56" s="7">
-        <v>899</v>
+        <v>19</v>
       </c>
       <c r="I56" s="7">
-        <v>41</v>
+        <v>-5</v>
       </c>
       <c r="J56" s="7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K56" s="7">
-        <v>-128</v>
+        <v>-253</v>
       </c>
       <c r="L56" s="7">
-        <v>5067</v>
+        <v>6651</v>
       </c>
       <c r="M56" s="7">
-        <v>899</v>
+        <v>1232</v>
       </c>
       <c r="N56" s="7">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="O56" s="7">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="P56" s="7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q56" s="7">
-        <v>1069</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -3005,49 +3011,49 @@
         <v>66</v>
       </c>
       <c r="C57" s="8">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="D57" s="8">
-        <v>1654</v>
+        <v>2120</v>
       </c>
       <c r="E57" s="8">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="F57" s="8">
-        <v>344</v>
+        <v>423</v>
       </c>
       <c r="G57" s="8">
-        <v>787</v>
+        <v>1224</v>
       </c>
       <c r="H57" s="8">
-        <v>72</v>
+        <v>899</v>
       </c>
       <c r="I57" s="8">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="J57" s="8">
-        <v>-3</v>
+        <v>16</v>
       </c>
       <c r="K57" s="8">
-        <v>345</v>
+        <v>-128</v>
       </c>
       <c r="L57" s="8">
-        <v>3371</v>
+        <v>5067</v>
       </c>
       <c r="M57" s="8">
-        <v>605</v>
+        <v>899</v>
       </c>
       <c r="N57" s="8">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O57" s="8">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="P57" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q57" s="8">
-        <v>770</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -3055,49 +3061,49 @@
         <v>67</v>
       </c>
       <c r="C58" s="7">
-        <v>769</v>
+        <v>18</v>
       </c>
       <c r="D58" s="7">
-        <v>1511</v>
+        <v>1654</v>
       </c>
       <c r="E58" s="7">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="F58" s="7">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="G58" s="7">
-        <v>603</v>
+        <v>787</v>
       </c>
       <c r="H58" s="7">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="I58" s="7">
-        <v>-16</v>
+        <v>62</v>
       </c>
       <c r="J58" s="7">
-        <v>24</v>
+        <v>-3</v>
       </c>
       <c r="K58" s="7">
-        <v>199</v>
+        <v>345</v>
       </c>
       <c r="L58" s="7">
-        <v>3578</v>
+        <v>3371</v>
       </c>
       <c r="M58" s="7">
-        <v>674</v>
+        <v>605</v>
       </c>
       <c r="N58" s="7">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="O58" s="7">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="P58" s="7">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="7">
-        <v>775</v>
+        <v>770</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -3105,49 +3111,49 @@
         <v>68</v>
       </c>
       <c r="C59" s="8">
-        <v>637</v>
+        <v>769</v>
       </c>
       <c r="D59" s="8">
-        <v>1214</v>
+        <v>1511</v>
       </c>
       <c r="E59" s="8">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="F59" s="8">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="G59" s="8">
-        <v>523</v>
+        <v>603</v>
       </c>
       <c r="H59" s="8">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I59" s="8">
-        <v>27</v>
+        <v>-16</v>
       </c>
       <c r="J59" s="8">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K59" s="8">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="L59" s="8">
-        <v>2982</v>
+        <v>3578</v>
       </c>
       <c r="M59" s="8">
-        <v>493</v>
+        <v>674</v>
       </c>
       <c r="N59" s="8">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O59" s="8">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="P59" s="8">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="Q59" s="8">
-        <v>615</v>
+        <v>775</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -3155,118 +3161,169 @@
         <v>69</v>
       </c>
       <c r="C60" s="7">
+        <v>637</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1214</v>
+      </c>
+      <c r="E60" s="7">
+        <v>108</v>
+      </c>
+      <c r="F60" s="7">
+        <v>307</v>
+      </c>
+      <c r="G60" s="7">
+        <v>523</v>
+      </c>
+      <c r="H60" s="7">
+        <v>80</v>
+      </c>
+      <c r="I60" s="7">
+        <v>27</v>
+      </c>
+      <c r="J60" s="7">
+        <v>19</v>
+      </c>
+      <c r="K60" s="7">
+        <v>67</v>
+      </c>
+      <c r="L60" s="7">
+        <v>2982</v>
+      </c>
+      <c r="M60" s="7">
+        <v>493</v>
+      </c>
+      <c r="N60" s="7">
+        <v>45</v>
+      </c>
+      <c r="O60" s="7">
+        <v>66</v>
+      </c>
+      <c r="P60" s="7">
+        <v>11</v>
+      </c>
+      <c r="Q60" s="7">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="18.1322" customHeight="1">
+      <c r="B61" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="8">
         <v>404</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D61" s="8">
         <v>1024</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E61" s="8">
         <v>104</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F61" s="8">
         <v>251</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G61" s="8">
         <v>474</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H61" s="8">
         <v>-2</v>
       </c>
-      <c r="I60" s="7">
+      <c r="I61" s="8">
         <v>20</v>
       </c>
-      <c r="J60" s="7">
+      <c r="J61" s="8">
         <v>12</v>
       </c>
-      <c r="K60" s="7">
+      <c r="K61" s="8">
         <v>32</v>
       </c>
-      <c r="L60" s="7">
+      <c r="L61" s="8">
         <v>2319</v>
       </c>
-      <c r="M60" s="7">
+      <c r="M61" s="8">
         <v>492</v>
       </c>
-      <c r="N60" s="7">
+      <c r="N61" s="8">
         <v>53</v>
       </c>
-      <c r="O60" s="7">
+      <c r="O61" s="8">
         <v>132</v>
       </c>
-      <c r="P60" s="7">
+      <c r="P61" s="8">
         <v>19</v>
       </c>
-      <c r="Q60" s="7">
+      <c r="Q61" s="8">
         <v>696</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="B61" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="10">
+    <row r="62" s="1" customFormat="1" ht="18.1322" customHeight="1">
+      <c r="B62" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="10">
         <v>355</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D62" s="10">
         <v>754</v>
       </c>
-      <c r="E61" s="10">
+      <c r="E62" s="10">
         <v>67</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F62" s="10">
         <v>207</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G62" s="10">
         <v>490</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H62" s="10">
         <v>105</v>
       </c>
-      <c r="I61" s="10">
+      <c r="I62" s="10">
         <v>68</v>
       </c>
-      <c r="J61" s="10">
+      <c r="J62" s="10">
         <v>14</v>
       </c>
-      <c r="K61" s="10">
+      <c r="K62" s="10">
         <v>50</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L62" s="10">
         <v>2110</v>
       </c>
-      <c r="M61" s="10">
+      <c r="M62" s="10">
         <v>509</v>
       </c>
-      <c r="N61" s="10">
+      <c r="N62" s="10">
         <v>38</v>
       </c>
-      <c r="O61" s="10">
+      <c r="O62" s="10">
         <v>69</v>
       </c>
-      <c r="P61" s="10">
+      <c r="P62" s="10">
         <v>-25</v>
       </c>
-      <c r="Q61" s="10">
+      <c r="Q62" s="10">
         <v>591</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
-    <row r="63" s="1" customFormat="1" ht="169.0561" customHeight="1">
-      <c r="B63" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-    </row>
+    <row r="63" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
+    <row r="64" s="1" customFormat="1" ht="169.0561" customHeight="1">
+      <c r="B64" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B64:H64"/>
   </mergeCells>
   <pageSetup paperSize="9" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
